--- a/data/trans_orig/Q5418_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>29285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22262</t>
+          <t>24861</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37495</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>39699</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>49794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>339883</t>
+          <t>377230</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>330655</t>
+          <t>366953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>347093</t>
+          <t>383922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>579686</t>
+          <t>406525</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>560892</t>
+          <t>397245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>596714</t>
+          <t>413931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>919569</t>
+          <t>783755</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>899431</t>
+          <t>770240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>947568</t>
+          <t>794278</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>366948</t>
+          <t>405792</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>366948</t>
+          <t>405792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366948</t>
+          <t>405792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>974906</t>
+          <t>844527</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974906</t>
+          <t>844527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>974906</t>
+          <t>844527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37861</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>49403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>86098</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>75055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91812</t>
+          <t>100543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>117247</t>
+          <t>125662</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102956</t>
+          <t>110332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132299</t>
+          <t>141035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35967</t>
+          <t>39058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28104</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69195</t>
+          <t>74743</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>63674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81494</t>
+          <t>86793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>113802</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91948</t>
+          <t>99167</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120452</t>
+          <t>129064</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>206119</t>
+          <t>228445</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>192920</t>
+          <t>215336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216179</t>
+          <t>240123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>276659</t>
+          <t>303122</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>262427</t>
+          <t>288826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290845</t>
+          <t>319331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>482779</t>
+          <t>531567</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>464460</t>
+          <t>510351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500776</t>
+          <t>550737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>705187</t>
+          <t>771030</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>705187</t>
+          <t>771030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705187</t>
+          <t>771030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>136607</t>
+          <t>146734</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163767</t>
+          <t>166209</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48469</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>114949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>134890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167801</t>
+          <t>171005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>546003</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>530481</t>
+          <t>589183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558940</t>
+          <t>620165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>856345</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>691578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>937782</t>
+          <t>728881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1402348</t>
+          <t>1315322</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1353126</t>
+          <t>1290698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1496653</t>
+          <t>1338615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
